--- a/data_extactor/batch_10_fa/batch_0056_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0056_fa.xlsx
@@ -508,27 +508,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>مانیتورینگ | سخن‌گفتن | استراتژی‌های یادگیری | گوش‌دادن فعال | تفکر انتقادی</t>
+          <t>نظارت | سخن گفتن | راهبردهای یادگیری | گوش دادن فعال | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | امنیت و ایمنی عمومی | زبان انگلیسی | آموزش و تربیت | پزشکی و دندانپزشکی</t>
+          <t>خدمات مشتری و شخصی | ایمنی و امنیت عمومی | زبان انگلیسی | آموزش و پرورش | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دید دور | بیان شفاهی | درک شفاهی | توجه انتخابی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری بستار | استدلال قیاسی | سرعت ادراکی | سرعت بستار | ترتیب‌دهی به اطلاعات | استدلال استقرایی | دید نزدیک | استقامت | قدرت بدنی | اشتراک زمانی</t>
+          <t>حساسیت به مسئله | بینایی دور | بیان شفاهی | درک شفاهی | توجه انتخابی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری بستار | استدلال قیاسی | سرعت ادراکی | سرعت بستار | ترتیب‌دهی اطلاعات | استدلال استقرایی | بینایی نزدیک | استقامت | قدرت تنه | تقسیم توجه</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>کار با یا کمک به یک گروه کاری یا تیم | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | سلامت و ایمنی سایر کارکنان | ایمیل | دفعات تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامد اشتباه | نزدیکی فیزیکی | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | داخل ساختمان، محیط کنترل‌شده | آزادی در تصمیم‌گیری | خارج از خانه، در معرض تمام شرایط آب‌وهوایی | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | مکالمات تلفنی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد</t>
+          <t>کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | سلامت و ایمنی سایر کارکنان | ایمیل | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامد خطا | نزدیکی فیزیکی | تعامل با مشتریان خارجی یا عموم مردم | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | فضای باز، در معرض تمام شرایط آب و هوایی | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | مکالمات تلفنی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>رانندگان و متصدیان آمبولانس، به‌جز تکنسین‌های فوریت‌های پزشکی | متصدیان تفریحی و شهربازی | مربیان ورزشی | غواصان تجاری | تکنسین‌های فوریت‌های پزشکی | مربیان ورزشی و مربیان تناسب اندام گروهی | بازرسان و کارآگاهان آتش‌نشانی | آتش‌نشانان | سرپرستان خط مقدم کارکنان سرگرمی و تفریحی، به‌جز خدمات قمار | سرپرستان خط مقدم کارکنان آتش‌نشانی و پیشگیری | سرپرستان خط مقدم کارکنان خدمات شخصی | بازرسان آتش‌سوزی جنگل و متخصصان پیشگیری | مهندسان ایمنی و بهداشت، به‌جز مهندسان و بازرسان ایمنی معدن | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های بهداشت و ایمنی شغلی | بهیاران | پارامدیک‌ها | کارکنان اجرای قوانین پارکینگ | کارکنان تفریحی | نگهبانان امنیتی</t>
+          <t>رانندگان و متصدیان آمبولانس، به جز تکنسین‌های فوریت‌های پزشکی | متصدیان تفریح و سرگرمی | مربیان ورزشی | غواصان تجاری | تکنسین‌های فوریت‌های پزشکی | مربیان ورزشی و مدرسان تناسب اندام گروهی | بازرسان و محققان آتش‌نشانی | آتش‌نشانان | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط اول آتش‌نشانی و پیشگیری | سرپرستان خط اول کارگران خدمات شخصی | بازرسان و متخصصان پیشگیری از آتش‌سوزی جنگل | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های بهداشت و ایمنی شغلی | بهیاران | پارامدیک‌ها | ماموران اجرای مقررات پارک | کارکنان تفریحات | نگهبانان امنیتی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>سخن‌گفتن | مانیتورینگ | تفکر انتقادی | گوش‌دادن فعال | درک مطلب</t>
+          <t>سخن گفتن | نظارت | تفکر انتقادی | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>امنیت و ایمنی عمومی | خدمات مشتریان و شخصی | زبان انگلیسی</t>
+          <t>ایمنی و امنیت عمومی | خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | توجه انتخابی | استدلال قیاسی | بیان شفاهی | درک شفاهی | انعطاف‌پذیری بستار | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | دید نزدیک | ترتیب‌دهی به اطلاعات | سرعت ادراکی | دید دور | انعطاف‌پذیری دسته‌بندی | درک کتبی | هماهنگی چند عضو بدن | چالاکی انگشتان | چالاکی دست</t>
+          <t>حساسیت به مسئله | توجه انتخابی | استدلال قیاسی | بیان شفاهی | درک شفاهی | انعطاف‌پذیری بستار | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | سرعت ادراکی | بینایی دور | انعطاف‌پذیری دسته‌بندی | درک کتبی | هماهنگی چند عضو | مهارت انگشتان | مهارت دستی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | داخل ساختمان، محیط کنترل‌شده | برخورد با افراد ناراحت، عصبانی یا بی‌ادب | کار با یا کمک به یک گروه کاری یا تیم | ارتباط با دیگران | نزدیکی فیزیکی | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا آزاردهنده | اهمیت دقیق یا درست بودن | صرف زمان به حالت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض آلاینده‌ها | ایمیل | پیامد اشتباه | دفعات تصمیم‌گیری | قرار گرفتن در معرض تابش | موقعیت‌های تعارض | اهمیت تکرار وظایف یکسان | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | محیط داخلی، دارای کنترل شرایط محیطی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | نزدیکی فیزیکی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت دقیق یا درست بودن | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض آلاینده‌ها | ایمیل | پیامد خطا | فراوانی تصمیم‌گیری | قرار گرفتن در معرض تابش | موقعیت‌های تعارض | اهمیت تکرار وظایف یکسان | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>کنترل‌کنندگان ترافیک هوایی | سرپرستان جابجایی بار هواپیما | متخصصان عملیات فرودگاه | باربران چمدان و پادوها | رانندگان اتوبوس، ترانزیت و بین‌شهری | افسران انطباق | ماموران عبور و پرچم‌داران | افسران گمرک و حفاظت مرزی | دیسپچرها، به‌جز پلیس، آتش‌نشانی و آمبولانس | سرپرستان خط مقدم کارکنان امنیتی | مهمانداران هواپیما | کارکنان اجرای قوانین پارکینگ | متصدیان مسافران | لوکوموتیورانان و مسئولان ایستگاه راه‌آهن | نمایندگان فروش بلیط رزرو و حمل و نقل و کارمندان سفر | نگهبانان امنیتی | متخصصان مدیریت امنیت | مدیران امنیت | اپراتورهای مترو و تراموا | پلیس ترانزیت و راه‌آهن</t>
+          <t>کنترلرهای ترافیک هوایی | سرپرستان جابجایی بار هواپیما | متخصصان عملیات فرودگاه | باربران چمدان و پادوهای هتل | رانندگان اتوبوس، ترانزیت و بین‌شهری | افسران انطباق | نگهبانان عبور و مرور و پرچم‌داران | ماموران گمرک و حفاظت مرزی | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | سرپرستان خط اول کارکنان امنیتی | مهمانداران هواپیما | ماموران اجرای مقررات پارک | متصدیان مسافران | رئیس قطارها و مدیران محوطه راه‌آهن | نمایندگان بلیط و رزرواسیون حمل و نقل و کارمندان سفر | نگهبانان امنیتی | متخصصان مدیریت امنیت | مدیران امنیتی | رانندگان مترو و تراموا | پلیس ترانزیت و راه‌آهن</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش‌دادن فعال | سخن‌گفتن | تفکر انتقادی | درک مطلب</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | امنیت و ایمنی عمومی | زبان انگلیسی | آموزش و تربیت | روانشناسی | حمل و نقل</t>
+          <t>خدمات مشتری و شخصی | ایمنی و امنیت عمومی | زبان انگلیسی | آموزش و پرورش | روان‌شناسی | حمل و نقل</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | ترتیب‌دهی به اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | اشتراک زمانی | چالاکی انگشتان | چالاکی دست | دید دور | حفظ کردن | روان بودن ایده‌ها | توجه شنیداری | زمان عکس‌العمل | قدرت بدنی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها | توجه شنیداری | زمان عکس‌العمل | قدرت ایستا</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>در یک وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | ارتباط با دیگران | نزدیکی فیزیکی | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | برخورد با افراد ناراحت، عصبانی یا بی‌ادب | سلامت و ایمنی سایر کارکنان | پیامد اشتباه | اهمیت تکرار وظایف یکسان | صرف زمان به حالت نشسته | صرف زمان به حالت ایستاده | دفعات تصمیم‌گیری | قرار گرفتن در معرض ارتعاش کل بدن | کار با یا کمک به یک گروه کاری یا تیم | فشار زمانی | خارج از خانه، در معرض تمام شرایط آب‌وهوایی</t>
+          <t>در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | ارتباط با دیگران | نزدیکی فیزیکی | تعامل با مشتریان خارجی یا عموم مردم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | سلامت و ایمنی سایر کارکنان | پیامد خطا | اهمیت تکرار وظایف یکسان | صرف زمان برای نشستن | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | قرار گرفتن در معرض ارتعاش کل بدن | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | فضای باز، در معرض تمام شرایط آب و هوایی</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>رانندگان اتوبوس مدرسه | رانندگان اتوبوس، ترانزیت و بین‌شهری | ماموران عبور و پرچم‌داران | دیسپچرها، به‌جز پلیس، آتش‌نشانی و آمبولانس | مدیران آموزشی، پیش‌دبستانی تا متوسطه | مشاوران و راهنمایان تحصیلی، شغلی و حرفه‌ای | معلمان دبستان، به‌جز آموزش استثنایی | مهمانداران هواپیما | متصدیان مسافران | لوکوموتیورانان و مسئولان ایستگاه راه‌آهن | روانشناسان مدرسه | رانندگان شاتل و شوفرها | معلمان آموزش استثنایی، دبستان | معلمان آموزش استثنایی، دبیرستان | اپراتورهای مترو و تراموا | رانندگان تاکسی | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و دبیرستان، به‌جز آموزش استثنایی | دستیاران آموزشی، آموزش استثنایی | پلیس ترانزیت و راه‌آهن | مدرسان خصوصی</t>
+          <t>رانندگان اتوبوس مدرسه | رانندگان اتوبوس، ترانزیت و بین‌شهری | نگهبانان عبور و مرور و پرچم‌داران | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | مدیران آموزشی، مهدکودک تا دبیرستان | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | معلمان دبستان، به استثنای آموزش استثنایی | مهمانداران هواپیما | متصدیان مسافران | رئیس قطارها و مدیران محوطه راه‌آهن | روان‌شناسان مدرسه | رانندگان شاتل و شوفرها | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، متوسطه | رانندگان مترو و تراموا | رانندگان تاکسی | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی | دستیاران آموزشی، آموزش استثنایی | پلیس ترانزیت و راه‌آهن | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>گوش‌دادن فعال | سخن‌گفتن | درک مطلب | تفکر انتقادی | مانیتورینگ | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>امنیت و ایمنی عمومی | خدمات مشتریان و شخصی | قانون و دولت | زبان انگلیسی | روانشناسی | کامپیوتر و الکترونیک | مخابرات</t>
+          <t>ایمنی و امنیت عمومی | خدمات مشتری و شخصی | قانون و دولت | زبان انگلیسی | روان‌شناسی | رایانه و الکترونیک | مخابرات</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | ترتیب‌دهی به اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | اشتراک زمانی | چالاکی انگشتان | چالاکی دست | دید دور | حفظ کردن | روان بودن ایده‌ها | زمان عکس‌العمل | قدرت بدنی | استقامت | توجه شنیداری | درک عمق</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها | زمان عکس‌العمل | قدرت ایستا | استقامت | توجه شنیداری | درک عمق</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | مکالمات تلفنی | پیامد اشتباه | دفعات تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | نزدیکی فیزیکی | برخورد با افراد ناراحت، عصبانی یا بی‌ادب | برخورد با افراد خشن یا متجاوز فیزیکی | صرف زمان به حالت ایستاده | صرف زمان به حالت پیاده‌روی یا دویدن | قرار گرفتن در معرض شرایط خطرناک | خارج از خانه، در معرض تمام شرایط آب‌وهوایی | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | کار با یا کمک به یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | فشار زمانی | ایمیل</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | مکالمات تلفنی | پیامد خطا | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | نزدیکی فیزیکی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | برخورد با افراد خشن یا از نظر فیزیکی پرخاشگر | صرف زمان برای ایستادن | صرف زمان برای راه رفتن یا دویدن | قرار گرفتن در معرض شرایط خطرناک | فضای باز، در معرض تمام شرایط آب و هوایی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | فشار زمانی | ایمیل</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>نگهبانان امنیتی | متخصصان پیشگیری از خسارت خرده‌فروشی | غربالگران امنیتی حمل و نقل | ماموران عبور و پرچم‌داران | نجات‌غریق‌ها، گشت اسکی و سایر کارکنان خدمات حفاظتی تفریحی | مراقبین اتوبوس مدرسه | کارکنان اجرای قوانین پارکینگ | کارکنان کنترل حیوانات | افسران نظارت بر قمار و کارآگاهان قمار | کارآگاهان و محققان خصوصی | افسران اصلاح و تربیت و زندانبانان | ضابطین دادگستری | ماموران گشت پلیس و کلانتر | پلیس ترانزیت و راه‌آهن | افسران گمرک و حفاظت مرزی | محیط‌بانان صید و شکار | آتش‌نشانان | سرپرستان خط مقدم کارکنان امنیتی | سرپرستان خط مقدم کارکنان خدمات حفاظتی، سایر | دیسپچرهای ایمنی عمومی</t>
+          <t>نگهبانان امنیتی | متخصصان پیشگیری از خسارت خرده‌فروشی | غربالگران امنیتی حمل و نقل | نگهبانان عبور و مرور و پرچم‌داران | نجات‌غریق‌ها، گشت اسکی و سایر کارکنان خدمات حفاظتی تفریحی | مراقبین اتوبوس مدرسه | ماموران اجرای مقررات پارک | کارکنان کنترل حیوانات | ماموران نظارت بر قمار و بازرسان قمار | کارآگاهان و بازرسان خصوصی | افسران اصلاح و تربیت و زندانبانان | ضابطان دادگستری | ماموران گشت پلیس و کلانتر | پلیس ترانزیت و راه‌آهن | ماموران گمرک و حفاظت مرزی | محیط‌بانان و جنگل‌بانان | آتش‌نشانان | سرپرستان خط اول کارکنان امنیتی | سرپرستان خط اول کارکنان خدمات حفاظتی، همه موارد دیگر | اپراتورهای مخابراتی امنیت عمومی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Aspect Loss Prevention Aspect EliteLP | Case management system software | نرم‌افزار پایگاه داده | Enterprise application integration EAI software | Epicor Loss Prevention | McAfee | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | NortonLifeLock cybersecurity software | Structured query language SQL</t>
+          <t>Aspect Loss Prevention Aspect EliteLP | نرم‌افزار سیستم مدیریت پرونده | نرم‌افزار پایگاه داده | نرم‌افزار یکپارچه‌سازی برنامه‌های کاربردی سازمانی EAI | Epicor Loss Prevention | McAfee | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | نرم‌افزار امنیت سایبری NortonLifeLock | زبان پرس‌وجوی ساختاریافته SQL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن‌گفتن | مانیتورینگ | گوش‌دادن فعال | یادگیری فعال | درک مطلب | نگارش</t>
+          <t>تفکر انتقادی | سخن گفتن | نظارت | گوش دادن فعال | یادگیری فعال | درک مطلب | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>امنیت و ایمنی عمومی | زبان انگلیسی | قانون و دولت | خدمات مشتریان و شخصی | آموزش و تربیت | مدیریت و سازماندهی | کامپیوتر و الکترونیک | پرسنل و منابع انسانی | اداری | ریاضیات</t>
+          <t>ایمنی و امنیت عمومی | زبان انگلیسی | قانون و دولت | خدمات مشتری و شخصی | آموزش و پرورش | مدیریت و اداره | رایانه و الکترونیک | پرسنل و منابع انسانی | اداری | ریاضیات</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | درک کتبی | دید نزدیک | توجه انتخابی | دید دور | ترتیب‌دهی به اطلاعات | انعطاف‌پذیری بستار | بیان کتبی | انعطاف‌پذیری دسته‌بندی</t>
+          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | درک کتبی | بینایی نزدیک | توجه انتخابی | بینایی دور | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | بیان کتبی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ارتباط با دیگران | کار با یا کمک به یک گروه کاری یا تیم | مکالمات تلفنی | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | داخل ساختمان، محیط کنترل‌شده | آزادی در تصمیم‌گیری | ایمیل | اهمیت دقیق یا درست بودن | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | دفعات تصمیم‌گیری | نزدیکی فیزیکی | سلامت و ایمنی سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | اهمیت تکرار وظایف یکسان | برخورد با افراد ناراحت، عصبانی یا بی‌ادب | موقعیت‌های تعارض | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سطح رقابت | پیامد اشتباه</t>
+          <t>ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | ایمیل | اهمیت دقیق یا درست بودن | تعامل با مشتریان خارجی یا عموم مردم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | نزدیکی فیزیکی | سلامت و ایمنی سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | اهمیت تکرار وظایف یکسان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | موقعیت‌های تعارض | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سطح رقابت | پیامد خطا</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>برنامه‌ریزان تداوم کسب‌وکار | مدیران انطباق | کارآگاهان و محققان جنایی | مدیران مدیریت بحران | متخصصان ریسک مالی | سرپرستان خط مقدم کارکنان امنیتی | ارزیابان، محققان و تحلیلگران تقلب | افسران نظارت بر قمار و کارآگاهان قمار | مهندسان ایمنی و بهداشت، به‌جز مهندسان و بازرسان ایمنی معدن | تحلیلگران امنیت اطلاعات | تحلیلگران اطلاعاتی | مدیران پیشگیری از خسارت | تحلیلگران مدیریت | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های بهداشت و ایمنی شغلی | تست‌کنندگان نفوذ | کارآگاهان و محققان خصوصی | نگهبانان امنیتی | متخصصان مدیریت امنیت | مدیران امنیت</t>
+          <t>برنامه‌ریزان تداوم کسب‌وکار | مدیران انطباق | کارآگاهان و بازرسان جنایی | مدیران مدیریت بحران | متخصصان ریسک مالی | سرپرستان خط اول کارکنان امنیتی | بازرسان، محققان و تحلیلگران کلاهبرداری | ماموران نظارت بر قمار و بازرسان قمار | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | تحلیل‌گران امنیت اطلاعات | تحلیلگران اطلاعاتی | مدیران پیشگیری از زیان | تحلیل‌گران مدیریت | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های بهداشت و ایمنی شغلی | کارشناسان آزمون نفوذ | کارآگاهان و بازرسان خصوصی | نگهبانان امنیتی | متخصصان مدیریت امنیت | مدیران امنیتی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>مانیتورینگ | سخن‌گفتن | تفکر انتقادی | گوش‌دادن فعال | درک مطلب | یادگیری فعال | استراتژی‌های یادگیری | نگارش | ریاضیات</t>
+          <t>نظارت | سخن گفتن | تفکر انتقادی | گوش دادن فعال | درک مطلب | یادگیری فعال | راهبردهای یادگیری | نگارش | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>تولید غذا | تولید و فرآوری | خدمات مشتریان و شخصی | پرسنل و منابع انسانی | مدیریت و سازماندهی | ریاضیات | آموزش و تربیت | زبان انگلیسی | اقتصاد و حسابداری | اداری</t>
+          <t>تولید مواد غذایی | تولید و فرآوری | خدمات مشتری و شخصی | پرسنل و منابع انسانی | مدیریت و اداره | ریاضیات | آموزش و پرورش | زبان انگلیسی | اقتصاد و حسابداری | اداری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | ترتیب‌دهی به اطلاعات | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | دید نزدیک | تشخیص گفتار | درک کتبی | اصالت | توجه انتخابی | روان بودن ایده‌ها | انعطاف‌پذیری دسته‌بندی | تجسم فضایی | اشتراک زمانی | قدرت بدنی | چالاکی انگشتان | چالاکی دست | ثبات بازو-دست | توانایی کار با اعداد | بیان کتبی | دید دور | استدلال ریاضی | تشخیص رنگ بصری | سرعت ادراکی | حفظ کردن | انعطاف‌پذیری بدنی</t>
+          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | ترتیب‌دهی اطلاعات | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | درک کتبی | اصالت | توجه انتخابی | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | تجسم | تقسیم توجه | قدرت تنه | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | توانایی عددی | بیان کتبی | بینایی دور | استدلال ریاضی | تشخیص رنگ بصری | سرعت ادراکی | حفظ کردن | انعطاف‌پذیری دامنه حرکت</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | داخل ساختمان، محیط کنترل‌شده | فشار زمانی | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک, دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان به حالت ایستاده | دفعات تصمیم‌گیری | ارتباط با دیگران | مکالمات تلفنی | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا کمک به یک گروه کاری یا تیم | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا آزاردهنده | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای انجام حرکات تکراری | نزدیکی فیزیکی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارکنان | نتایج کار و عملکرد سایر کارکنان | قرار گرفتن در معرض تجهیزات خطرناک | سطح رقابت | برخورد با افراد ناراحت، عصبانی یا بی‌ادب | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت تکرار وظایف یکسان | نامه‌ها و یادداشت‌های مکتوب | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | قرار گرفتن در معرض آلاینده‌ها | موقعیت‌های تعارض | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | فشار زمانی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | ارتباط با دیگران | مکالمات تلفنی | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای انجام حرکات تکراری | نزدیکی فیزیکی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارکنان | پیامدهای کاری و نتایج سایر کارکنان | قرار گرفتن در معرض تجهیزات خطرناک | سطح رقابت | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت تکرار وظایف یکسان | نامه‌ها و یادداشت‌های کتبی | تعامل با مشتریان خارجی یا عموم مردم | قرار گرفتن در معرض آلاینده‌ها | موقعیت‌های تعارض | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>نانوایان | باریستاها | قصابان و قطعه‌کنندگان گوشت | آشپزهای غذای آماده | آشپزهای موسسات و سلف‌سرویس‌ها | آشپزهای خانگی خصوصی | آشپزهای رستوران | آشپزهای سفارشات سریع | تکنسین‌های تغذیه | متصدیان سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | کارکنان غذای آماده و کانتر | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | دست‌اندرکاران پخت انبوه غذا | اپراتورها و متصدیان دستگاه‌های پخت غذا | کارکنان تهیه غذا | سروکنندگان غذا، غیررستورانی | مدیران خدمات غذایی | اپراتورها و متصدیان دستگاه‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | میزبانان رستوران، سالن و کافی‌شاپ | گارسون‌ها و پیشخدمت‌ها</t>
+          <t>نانوایان | باریستاها | قصابان و برش‌دهندگان گوش | آشپزهای غذای آماده | آشپزهای موسسات و سلف‌سرویس‌ها | آشپزهای خانگی خصوصی | آشپزها، رستوران | آشپزها، سفارش‌های فوری | تکنسین‌های رژیم غذایی | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | کارگران فست فود و پیشخوان | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | بچ‌سازان مواد غذایی | اپراتورها و متصدیان ماشین‌های پخت مواد غذایی | کارگران آماده‌سازی مواد غذایی | سروکنندگان غذا، غیررستورانی | مدیران خدمات غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | میزبانان رستوران، سالن و کافی‌شاپ | پیشخدمت‌ها و گارسون‌ها</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>سخن‌گفتن | مانیتورینگ | گوش‌دادن فعال | درک مطلب | تفکر انتقادی | استراتژی‌های یادگیری | یادگیری فعال | ریاضیات | نگارش</t>
+          <t>سخن گفتن | نظارت | گوش دادن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | ریاضیات | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | مدیریت و سازماندهی | تولید غذا | زبان انگلیسی | تولید و فرآوری | بازاریابی و فروش | آموزش و تربیت | پرسنل و منابع انسانی</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | تولید مواد غذایی | زبان انگلیسی | تولید و فرآوری | فروش و بازاریابی | آموزش و پرورش | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | درک کتبی | دید نزدیک | قدرت بدنی | اشتراک زمانی | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی به اطلاعات | استدلال استقرایی | روان بودن ایده‌ها | بیان کتبی | دید دور</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | درک کتبی | بینایی نزدیک | قدرت تنه | تقسیم توجه | توجه انتخابی | تجسم | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | روانی ایده‌ها | بیان کتبی | بینایی دور</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | داخل ساختمان، محیط کنترل‌شده | ارتباط با دیگران | کار با یا کمک به یک گروه کاری یا تیم | نزدیکی فیزیکی | اهمیت دقیق یا درست بودن | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | سلامت و ایمنی سایر کارکنان | صرف زمان به حالت ایستاده | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | نتایج کار و عملکرد سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | اهمیت تکرار وظایف یکسان | سخنرانی عمومی</t>
+          <t>مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | اهمیت دقیق یا درست بودن | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سلامت و ایمنی سایر کارکنان | صرف زمان برای ایستادن | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | پیامدهای کاری و نتایج سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | اهمیت تکرار وظایف یکسان | سخنرانی عمومی</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>سرآشپزها و آشپزهای ارشد | متصدیان سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | کارکنان غذای آماده و کانتر | سرپرستان خط مقدم مشاغل ساختمانی و استخراج | سرپرستان خط مقدم کارکنان سرگرمی و تفریحی، به‌جز خدمات قمار | سرپرستان خط مقدم کارکنان کشاورزی، ماهیگیری و جنگلداری | سرپرستان خط مقدم دستیاران، کارگران و جابجا‌کنندگان دستی مواد | سرپرستان خط مقدم کارکنان خانه‌داری و سرایداری | سرپرستان خط مقدم کارکنان محوطه‌سازی، خدمات چمن و نگهداری فضای سبز | سرپرستان خط مقدم اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط مقدم مکانیک‌ها، نصب‌کنندگان و تعمیرکاران | سرپرستان خط مقدم کارکنان فروش غیرخرده‌فروشی | سرپرستان خط مقدم کارکنان پشتیبانی اداری و دفتری | سرپرستان خط مقدم متصدیان مسافران | سرپرستان خط مقدم کارکنان خدمات شخصی | سرپرستان خط مقدم کارکنان تولید و عملیات | سرپرستان خط مقدم کارکنان فروش خرده‌فروشی | کارکنان تهیه غذا | مدیران خدمات غذایی | مدیران کل و عملیاتی</t>
+          <t>سرآشپزها و آشپزهای ارشد | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | کارگران فست فود و پیشخوان | سرپرستان خط اول مشاغل ساختمانی و کارگران استخراج | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول کارگران فضای سبز، خدمات چمن‌زنی و نگهداری محوطه | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | سرپرستان خط اول مهمانداران مسافری | سرپرستان خط اول کارگران خدمات شخصی | سرپرستان رده اول کارگران تولید و بهره‌برداری | سرپرستان رده اول کارکنان فروش خرده‌فروشی | کارگران آماده‌سازی مواد غذایی | مدیران خدمات غذایی | مدیران عمومی و عملیات</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>گوش‌دادن فعال</t>
+          <t>گوش دادن فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مدیریت و سازماندهی | حمل و نقل | ارتباطات و رسانه | خدمات مشتریان و شخصی | امنیت و ایمنی عمومی | زبان انگلیسی</t>
+          <t>مدیریت و اداره | حمل و نقل | ارتباطات و رسانه | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | دید نزدیک | ترتیب‌دهی به اطلاعات | تشخیص گفتار</t>
+          <t>درک شفاهی | بینایی نزدیک | ترتیب‌دهی اطلاعات | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان به حالت ایستاده | اهمیت دقیق یا درست بودن | پیامد اشتباه | کار با یا کمک به یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با افراد ناراحت، عصبانی یا بی‌ادب | نزدیکی فیزیکی | مکالمات تلفنی | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای ایستادن | اهمیت دقیق یا درست بودن | پیامد خطا | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | نزدیکی فیزیکی | مکالمات تلفنی | تعامل با مشتریان خارجی یا عموم مردم</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>نانوایان | باریستاها | قصابان و قطعه‌کنندگان گوشت | سرآشپزها و آشپزهای ارشد | آشپزهای موسسات و سلف‌سرویس‌ها | آشپزهای خانگی خصوصی | آشپزهای رستوران | آشپزهای سفارشات سریع | متصدیان سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | ظرفشورها | کارکنان غذای آماده و کانتر | دست‌اندرکاران پخت انبوه غذا | اپراتورها و متصدیان دستگاه‌های پخت غذا | کارکنان تهیه غذا | سروکنندگان غذا، غیررستورانی | مدیران خدمات غذایی | اپراتورها و متصدیان دستگاه‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | درجه‌بندها و سورترهای محصولات کشاورزی | برش‌دهندگان و پاک‌کنندگان گوشت، مرغ و ماهی | گارسون‌ها و پیشخدمت‌ها</t>
+          <t>نانوایان | باریستاها | قصابان و برش‌دهندگان گوش | سرآشپزها و آشپزهای ارشد | آشپزهای موسسات و سلف‌سرویس‌ها | آشپزهای خانگی خصوصی | آشپزها، رستوران | آشپزها، سفارش‌های فوری | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | ظرف‌شوی‌ها | کارگران فست فود و پیشخوان | بچ‌سازان مواد غذایی | اپراتورها و متصدیان ماشین‌های پخت مواد غذایی | کارگران آماده‌سازی مواد غذایی | سروکنندگان غذا، غیررستورانی | مدیران خدمات غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | درجه‌بندها و مرتب‌کنندگان محصولات کشاورزی | برش‌دهندگان و پاک‌کنندگان گوشت، مرغ و ماهی | پیشخدمت‌ها و گارسون‌ها</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>سخن‌گفتن | مانیتورینگ | تفکر انتقادی | گوش‌دادن فعال</t>
+          <t>سخن گفتن | نظارت | تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | تولید غذا | خدمات مشتریان و شخصی | ریاضیات | مدیریت و سازماندهی | تولید و فرآوری</t>
+          <t>زبان انگلیسی | تولید مواد غذایی | خدمات مشتری و شخصی | ریاضیات | مدیریت و اداره | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | دید نزدیک | وضوح گفتار | حساسیت به مسئله | درک شفاهی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی به اطلاعات | استدلال قیاسی | تجسم فضایی | استدلال استقرایی | درک کتبی | تشخیص گفتار | قدرت بدنی | چالاکی انگشتان | چالاکی دست | ثبات بازو-دست | اشتراک زمانی | توجه انتخابی</t>
+          <t>بیان شفاهی | بینایی نزدیک | وضوح گفتار | حساسیت به مسئله | درک شفاهی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی | تجسم | استدلال استقرایی | درک کتبی | تشخیص گفتار | قدرت تنه | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | تقسیم توجه | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان به حالت ایستاده | داخل ساختمان، محیط کنترل‌شده | ارتباط با دیگران | کار با یا کمک به یک گروه کاری یا تیم | فشار زمانی | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | صرف زمان به حالت پیاده‌روی یا دویدن | سلامت و ایمنی سایر کارکنان | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | نزدیکی فیزیکی | دفعات تصمیم‌گیری | نتایج کار و عملکرد سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای انجام حرکات تکراری | آزادی در تصمیم‌گیری | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا آزاردهنده</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای ایستادن | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | صرف زمان برای راه رفتن یا دویدن | سلامت و ایمنی سایر کارکنان | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | نزدیکی فیزیکی | فراوانی تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای انجام حرکات تکراری | آزادی در تصمیم‌گیری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>نانوایان | باریستاها | قصابان و قطعه‌کنندگان گوشت | سرآشپزها و آشپزهای ارشد | آشپزهای غذای آماده | آشپزهای خانگی خصوصی | آشپزهای رستوران | آشپزهای سفارشات سریع | تکنسین‌های تغذیه | متصدیان سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | ظرفشورها | کارکنان غذای آماده و کانتر | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | دست‌اندرکاران پخت انبوه غذا | اپراتورها و متصدیان دستگاه‌های پخت غذا | کارکنان تهیه غذا | سروکنندگان غذا، غیررستورانی | مدیران خدمات غذایی | اپراتورها و متصدیان دستگاه‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | گارسون‌ها و پیشخدمت‌ها</t>
+          <t>نانوایان | باریستاها | قصابان و برش‌دهندگان گوش | سرآشپزها و آشپزهای ارشد | آشپزهای غذای آماده | آشپزهای خانگی خصوصی | آشپزها، رستوران | آشپزها، سفارش‌های فوری | تکنسین‌های رژیم غذایی | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | ظرف‌شوی‌ها | کارگران فست فود و پیشخوان | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | بچ‌سازان مواد غذایی | اپراتورها و متصدیان ماشین‌های پخت مواد غذایی | کارگران آماده‌سازی مواد غذایی | سروکنندگان غذا، غیررستورانی | مدیران خدمات غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | پیشخدمت‌ها و گارسون‌ها</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | مانیتورینگ | سخن‌گفتن | گوش‌دادن فعال | درک مطلب</t>
+          <t>تفکر انتقادی | نظارت | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | تولید غذا | بازاریابی و فروش | مدیریت و سازماندهی | تولید و فرآوری | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | تولید مواد غذایی | فروش و بازاریابی | مدیریت و اداره | تولید و فرآوری | ریاضیات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>دید نزدیک | روان بودن ایده‌ها | حساسیت به مسئله | چالاکی انگشتان | چالاکی دست | ترتیب‌دهی به اطلاعات | استدلال قیاسی | بیان شفاهی | اصالت | درک کتبی | درک شفاهی | تشخیص گفتار | قدرت بدنی | ثبات بازو-دست | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی</t>
+          <t>بینایی نزدیک | روانی ایده‌ها | حساسیت به مسئله | مهارت انگشتان | مهارت دستی | ترتیب‌دهی اطلاعات | استدلال قیاسی | بیان شفاهی | اصالت | درک کتبی | درک شفاهی | تشخیص گفتار | قدرت تنه | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>صرف زمان به حالت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ایمیل | فشار زمانی | آزادی در تصمیم‌گیری | داخل ساختمان، محیط کنترل‌شده | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | صرف زمان برای انجام حرکات تکراری | ارتباط با دیگران | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن</t>
+          <t>صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ایمیل | فشار زمانی | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | صرف زمان برای انجام حرکات تکراری | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>نانوایان | باریستاها | بارتندرها | قصابان و قطعه‌کنندگان گوشت | سرآشپزها و آشپزهای ارشد | آشپزهای غذای آماده | آشپزهای موسسات و سلف‌سرویس‌ها | آشپزهای رستوران | آشپزهای سفارشات سریع | تکنسین‌های تغذیه | متصدیان سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | ظرفشورها | کارکنان غذای آماده و کانتر | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | کارکنان تهیه غذا | دانشمندان و تکنولوژیست‌های مواد غذایی | سروکنندگان غذا، غیررستورانی | مدیران خدمات غذایی | میزبانان رستوران، سالن و کافی‌شاپ | گارسون‌ها و پیشخدمت‌ها</t>
+          <t>نانوایان | باریستاها | بارتندرها | قصابان و برش‌دهندگان گوش | سرآشپزها و آشپزهای ارشد | آشپزهای غذای آماده | آشپزهای موسسات و سلف‌سرویس‌ها | آشپزها، رستوران | آشپزها، سفارش‌های فوری | تکنسین‌های رژیم غذایی | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | ظرف‌شوی‌ها | کارگران فست فود و پیشخوان | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | کارگران آماده‌سازی مواد غذایی | دانشمندان و تکنولوژیست‌های علوم غذایی | سروکنندگان غذا، غیررستورانی | مدیران خدمات غذایی | میزبانان رستوران، سالن و کافی‌شاپ | پیشخدمت‌ها و گارسون‌ها</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0056_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0056_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | راهبردهای یادگیری | شنیدن فعال | تفکر انتقادی</t>
+          <t>نظارت | سخن گفتن | راهبردهای یادگیری | گوش دادن فعال | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | زبان انگلیسی | آموزش و تدریس | پزشکی و دندانپزشکی</t>
+          <t>خدمات مشتری و شخصی | ایمنی و امنیت عمومی | زبان انگلیسی | آموزش و پرورش | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دید دور | بیان شفاهی | درک شفاهی | توجه انتخابی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری بستار | استدلال قیاسی | سرعت ادراک | سرعت بستار | مرتب‌سازی اطلاعات | استدلال استقرایی | دید نزدیک | استقامت بدنی | قدرت عضلات تنه | تسهیم توجه</t>
+          <t>حساسیت به مسئله | بینایی دور | بیان شفاهی | درک شفاهی | توجه انتخابی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری بستار | استدلال قیاسی | سرعت ادراکی | سرعت بستار | ترتیب‌دهی اطلاعات | استدلال استقرایی | بینایی نزدیک | استقامت | قدرت تنه | تقسیم توجه</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>رانندگان و متصدیان آمبولانس (به‌جز تکنسین‌های فوریت‌های پزشکی) | متصدیان اماکن تفریحی و سرگرمی | مربیان ورزشی | غواصان تجاری و صنعتی | تکنسین‌های فوریت‌های پزشکی (EMT) | مربیان ورزش و تناسب اندام گروهی | بازرسان و کارشناسان بررسی حریق | آتش‌نشانان | سرپرستان رده‌اول کارکنان تفریحی و سرگرمی (به‌جز خدمات شرط‌بندی) | سرپرستان رده‌اول کارکنان آتش‌نشانی و پیشگیری از حریق | سرپرستان رده‌اول کارکنان خدمات فردی | بازرسان و کارشناسان پیشگیری از حریق جنگل‌ها | مهندسان بهداشت و ایمنی حرفه‌ای (به‌جز مهندسان و بازرسان ایمنی معدن) | کارشناسان بهداشت و ایمنی حرفه‌ای | کاردان‌های فنی بهداشت و ایمنی حرفه‌ای | نیروهای خدمات بیمارستانی و برانکاردبران | پیراپزشکان فوریت‌های پزشکی | ماموران نظارت و کنترل پارک خودرو | کارکنان امور تفریحی و اوقات فراغت | نگهبانان و ماموران حراست</t>
+          <t>رانندگان و خدمه آمبولانس، به‌جز تکنسین‌های فوریت‌های پزشکی | متصدیان اماکن تفریحی و شهربازی | مربیان و متخصصان سلامت و توان‌بخشی ورزشی | غواصان تجاری و صنعتی | تکنسین‌های فوریت‌های پزشکی | مربیان ورزش و آمادگی جسمانی گروهی | بازرسان و کارشناسان بررسی علل حریق | آتش‌نشانان | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | بازرسان و کارشناسان پیشگیری از حریق جنگل | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کاردان‌ها و تکنسین‌های بهداشت حرفه‌ای و ایمنی کار | خدمات‌دهندگان و انتقال‌دهندگان بیمار | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | ماموران کنترل و اعمال قانون پارک دوبله و توقف | کارکنان و متصدیان امور تفریحی و اوقات فراغت | نگهبانان و ماموران حراست</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>سخن گفتن | نظارت | تفکر انتقادی | شنیدن فعال | درک مطلب</t>
+          <t>سخن گفتن | نظارت | تفکر انتقادی | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | زبان انگلیسی</t>
+          <t>ایمنی و امنیت عمومی | خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | توجه انتخابی | استدلال قیاسی | بیان شفاهی | درک شفاهی | انعطاف‌پذیری بستار | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | دید نزدیک | مرتب‌سازی اطلاعات | سرعت ادراک | دید دور | انعطاف‌پذیری طبقه‌بندی | درک کتبی | هماهنگی اندام‌ها | چابکی انگشتان | چابکی دستی</t>
+          <t>حساسیت به مسئله | توجه انتخابی | استدلال قیاسی | بیان شفاهی | درک شفاهی | انعطاف‌پذیری بستار | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | سرعت ادراکی | بینایی دور | انعطاف‌پذیری دسته‌بندی | درک کتبی | هماهنگی چند عضو | مهارت انگشتان | مهارت دستی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>کنترلرهای ترافیک هوایی | سرپرستان جابه‌جایی بار هواپیما | کارشناسان عملیات فرودگاهی | باربران و متصدیان جابه‌جایی بار | رانندگان اتوبوس‌های شهری و بین‌شهری | کارشناسان ارزیابی انطباق با مقررات | ماموران هدایت ترافیک و نگهبانان تقاطع | افسران گمرک و حفاظت مرزی | دیسپچرهای حمل‌ونقل (به‌جز پلیس، آتش‌نشانی و اورژانس) | سرپرستان رده‌اول نیروهای حراست و نگهبانی | مهمانداران هواپیما | ماموران نظارت و کنترل پارک خودرو | مهمانداران و متصدیان خدمات مسافری | رئیسان قطار و سرپرستان توقفگاه‌های راه‌آهن | متصدیان رزرو، صدور بلیت و خدمات سفر | نگهبانان و ماموران حراست | کارشناسان مدیریت امور حفاظتی و امنیتی | مدیران حراست و امنیت | راهبران قطار شهری و تراموا | پلیس مترو و راه‌آهن</t>
+          <t>کنترلرهای ترافیک هوایی | سرپرستان بارگیری و جابه‌جایی بار هواپیما | کارشناسان عملیات فرودگاهی | متصدیان حمل بار و خدمات هتل | رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | کارشناسان پایش انطباق و بازرسی مقرراتی | نگهبانان عبور و مرور و پرچم‌داران ترافیکی | ماموران گمرک و حفاظت مرزی | متصدیان دیسپاچ و اعزام | سرپرستان رده‌اول کارکنان حراست و انتظامات | مهمانداران هواپیما | ماموران کنترل و اعمال قانون پارک دوبله و توقف | مهمانداران و متصدیان خدمات مسافران | رؤسای قطار و مدیران محوطه راه‌آهن | متصدیان فروش بلیت، رزرواسیون و خدمات سفر | نگهبانان و ماموران حراست | کارشناسان مدیریت حراست و امنیت فیزیکی | مدیران حراست و انتظامات | رانندگان مترو و تراموا | پلیس ترانزیت و راه‌آهن</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | زبان انگلیسی | آموزش و تدریس | روان‌شناسی | ترابری و حمل‌ونقل</t>
+          <t>خدمات مشتری و شخصی | ایمنی و امنیت عمومی | زبان انگلیسی | آموزش و پرورش | روان‌شناسی | حمل و نقل</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | تسهیم توجه | چابکی انگشتان | چابکی دستی | دید دور | حافظه | روانی بیان ایده‌ها | توجه شنیداری | زمان واکنش | قدرت ایستایی عضلانی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها | توجه شنیداری | زمان عکس‌العمل | قدرت ایستا</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>رانندگان اتوبوس مدارس | رانندگان اتوبوس‌های شهری و بین‌شهری | ماموران هدایت ترافیک و نگهبانان تقاطع | دیسپچرهای حمل‌ونقل (به‌جز پلیس، آتش‌نشانی و اورژانس) | مدیران آموزشی پیش‌دبستانی تا متوسطه | مشاوران و راهنمایان تحصیلی، تربیتی و شغلی | آموزگاران دوره ابتدایی (به‌جز آموزش استثنایی) | مهمانداران هواپیما | مهمانداران و متصدیان خدمات مسافری | رئیسان قطار و سرپرستان توقفگاه‌های راه‌آهن | روان‌شناسان مدرسه | رانندگان خودروهای سرویس و تشریفات | معلمان دوره ابتدایی آموزش استثنایی | معلمان دوره متوسطه آموزش استثنایی | راهبران قطار شهری و تراموا | رانندگان تاکسی | دستیاران آموزشی دوره‌های پیش‌دبستانی تا متوسطه | دستیاران آموزشی مدارس استثنایی | پلیس مترو و راه‌آهن | مربیان و معلمان خصوصی</t>
+          <t>رانندگان سرویس مدارس | رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | نگهبانان عبور و مرور و پرچم‌داران ترافیکی | متصدیان دیسپاچ و اعزام | مدیران آموزشی مقاطع ابتدایی و متوسطه | مشاوران تحصیلی، شغلی و هدایت استعدادها | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | مهمانداران هواپیما | مهمانداران و متصدیان خدمات مسافران | رؤسای قطار و مدیران محوطه راه‌آهن | روان‌شناسان مدارس | رانندگان خودروهای سرویس و تشریفات | معلمان آموزش استثنایی دوره ابتدایی | دبیران آموزش استثنایی دوره دوم متوسطه | رانندگان مترو و تراموا | رانندگان تاکسی | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی) | کمک‌معلمان آموزش استثنایی | پلیس ترانزیت و راه‌آهن | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | امور حقوقی و دولتی | زبان انگلیسی | روان‌شناسی | رایانه و الکترونیک | مخابرات و ارتباطات</t>
+          <t>ایمنی و امنیت عمومی | خدمات مشتری و شخصی | قانون و دولت | زبان انگلیسی | روان‌شناسی | رایانه و الکترونیک | مخابرات</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | تسهیم توجه | چابکی انگشتان | چابکی دستی | دید دور | حافظه | روانی بیان ایده‌ها | زمان واکنش | قدرت ایستایی عضلانی | استقامت بدنی | توجه شنیداری | ادراک عمق</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها | زمان عکس‌العمل | قدرت ایستا | استقامت | توجه شنیداری | درک عمق</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>نگهبانان و ماموران حراست | کارشناسان پیشگیری از سرقت و افت کالا در خرده‌فروشی‌ها | ماموران بازرسی و کنترل امنیتی حمل‌ونقل | ماموران هدایت ترافیک و نگهبانان تقاطع | ناجیان غریق، گشت اسکی و سایر مشاغل خدمات حفاظتی و امدادی تفریحی | مراقبین و متصدیان سرویس مدارس | ماموران نظارت و کنترل پارک خودرو | ماموران کنترل حیوانات | ماموران نظارت تصویری و بازرسان مراکز سرگرمی | کارآگاهان و بازرسان خصوصی | افسران و زندانبانان مراکز اصلاح و تربیت | ضابطان قضایی دادگاه | افسران گشت پلیس و ماموران انتظامی | پلیس مترو و راه‌آهن | افسران گمرک و حفاظت مرزی | محیط‌بانان و حافظان شیلات | آتش‌نشانان | سرپرستان رده‌اول نیروهای حراست و نگهبانی | سرپرستان رده‌اول سایر نیروهای خدمات حفاظتی | متصدیان ارتباطات و دیسپچرهای فوریت‌های عمومی</t>
+          <t>نگهبانان و ماموران حراست | کارشناسان پیشگیری از سرقت و افت کالا در خرده‌فروشی‌ها | ماموران بازرسی و کنترل امنیتی حمل‌ونقل | نگهبانان عبور و مرور و پرچم‌داران ترافیکی | ناجیان غریق، گشت اسکی و سایر مشاغل خدمات حفاظتی و امدادی تفریحی | مراقبین و متصدیان سرویس مدارس | ماموران کنترل و اعمال قانون پارک دوبله و توقف | ماموران کنترل و ساماندهی حیوانات | ماموران و بازرسان نظارت تصویری و پایش اماکن سرگرمی و بازی | کارآگاهان و بازرسان خصوصی | مأموران زندان و بازداشتگاه | مأموران انتظامات و حفاظت دادگاه | ماموران گشت پلیس و کلانتری | پلیس ترانزیت و راه‌آهن | ماموران گمرک و حفاظت مرزی | محیط‌بانان و ماموران حفاظت شیلات و حیات وحش | آتش‌نشانان | سرپرستان رده‌اول کارکنان حراست و انتظامات | سرپرستان رده‌اول کارکنان خدمات حفاظتی، سایر مشاغل | اپراتورهای فوریت‌های پلیسی و امدادی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | نظارت | شنیدن فعال | یادگیری فعال | درک مطلب | نگارش</t>
+          <t>تفکر انتقادی | سخن گفتن | نظارت | گوش دادن فعال | یادگیری فعال | درک مطلب | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | زبان انگلیسی | امور حقوقی و دولتی | خدمات مشتریان و خدمات فردی | آموزش و تدریس | مدیریت و امور اداری | رایانه و الکترونیک | پرسنلی و منابع انسانی | اداری و دفتری | ریاضیات</t>
+          <t>ایمنی و امنیت عمومی | زبان انگلیسی | قانون و دولت | خدمات مشتری و شخصی | آموزش و پرورش | مدیریت و اداره | رایانه و الکترونیک | پرسنل و منابع انسانی | اداری | ریاضیات</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | درک کتبی | دید نزدیک | توجه انتخابی | دید دور | مرتب‌سازی اطلاعات | انعطاف‌پذیری بستار | بیان کتبی | انعطاف‌پذیری طبقه‌بندی</t>
+          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | درک کتبی | بینایی نزدیک | توجه انتخابی | بینایی دور | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | بیان کتبی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کارشناسان برنامه‌ریزی تداوم کسب‌وکار | مدیران ارزیابی انطباق با قوانین | کارآگاهان و بازرسان جنایی | مدیران مدیریت بحران | کارشناسان ریسک مالی | سرپرستان رده‌اول نیروهای حراست و نگهبانی | کارشناسان بررسی، بازرسی و تحلیل تقلب | ماموران نظارت تصویری و بازرسان مراکز سرگرمی | مهندسان بهداشت و ایمنی حرفه‌ای (به‌جز مهندسان و بازرسان ایمنی معدن) | تحلیل‌گران امنیت اطلاعات | تحلیل‌گران اطلاعات و امنیت | مدیران پیشگیری از افت و خسارت کالا | تحلیل‌گران و کارشناسان بهبود مدیریت | کارشناسان بهداشت و ایمنی حرفه‌ای | کاردان‌های فنی بهداشت و ایمنی حرفه‌ای | کارشناسان آزمون نفوذپذیری سامانه‌ها | کارآگاهان و بازرسان خصوصی | نگهبانان و ماموران حراست | کارشناسان مدیریت امور حفاظتی و امنیتی | مدیران حراست و امنیت</t>
+          <t>کارشناسان برنامه‌ریزی تداوم کسب‌وکار | مدیران تطبیق و نظارت مقرراتی | کارآگاهان و بازرسان جنایی | مدیران مدیریت بحران و پدافند غیرعامل | کارشناسان ریسک مالی | سرپرستان رده‌اول کارکنان حراست و انتظامات | کارشناسان بازرسی، کشف و تحلیل تقلب | ماموران و بازرسان نظارت تصویری و پایش اماکن سرگرمی و بازی | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | تحلیل‌گران امنیت اطلاعات | تحلیل‌گران داده‌ها و اطلاعات امنیتی | مدیران پیشگیری از اتلاف منابع و صیانت از دارایی‌ها | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کاردان‌ها و تکنسین‌های بهداشت حرفه‌ای و ایمنی کار | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | کارآگاهان و بازرسان خصوصی | نگهبانان و ماموران حراست | کارشناسان مدیریت حراست و امنیت فیزیکی | مدیران حراست و انتظامات</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | تفکر انتقادی | شنیدن فعال | درک مطلب | یادگیری فعال | راهبردهای یادگیری | نگارش | ریاضیات</t>
+          <t>نظارت | سخن گفتن | تفکر انتقادی | گوش دادن فعال | درک مطلب | یادگیری فعال | راهبردهای یادگیری | نگارش | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>تولید مواد غذایی | تولید و فرآوری | خدمات مشتریان و خدمات فردی | پرسنلی و منابع انسانی | مدیریت و امور اداری | ریاضیات | آموزش و تدریس | زبان انگلیسی | اقتصاد و حسابداری | اداری و دفتری</t>
+          <t>تولید مواد غذایی | تولید و فرآوری | خدمات مشتری و شخصی | پرسنل و منابع انسانی | مدیریت و اداره | ریاضیات | آموزش و پرورش | زبان انگلیسی | اقتصاد و حسابداری | اداری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | مرتب‌سازی اطلاعات | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | دید نزدیک | تشخیص گفتار | درک کتبی | خلاقیت و ابتکار | توجه انتخابی | روانی بیان ایده‌ها | انعطاف‌پذیری طبقه‌بندی | تجسم فضایی | تسهیم توجه | قدرت عضلات تنه | چابکی انگشتان | چابکی دستی | ثبات و تسلط دست و بازو | مهارت محاسبات عددی | بیان کتبی | دید دور | استدلال ریاضی | تشخیص رنگ‌ها | سرعت ادراک | حافظه | دامنه انعطاف‌پذیری بدن</t>
+          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | ترتیب‌دهی اطلاعات | وضوح گفتار | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | درک کتبی | اصالت | توجه انتخابی | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | تجسم | تقسیم توجه | قدرت تنه | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | توانایی عددی | بیان کتبی | بینایی دور | استدلال ریاضی | تشخیص رنگ بصری | سرعت ادراکی | حفظ کردن | انعطاف‌پذیری دامنه حرکت</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>نانوایان و شیرینی‌پزان | باریستاها | قصابان و خردکنندگان گوشت | آشپزان فست‌فود | آشپزان مراکز پخت گروهی و سلف‌سرویس‌ها | آشپزان منازل مسکونی | آشپزان رستوران‌ها | آشپزان غذاهای فوری | کاردان‌های فنی تغذیه | کارگران سالن پذیرایی، سلف‌سرویس و کمک‌متصدیان بار | کارکنان فست‌فود و پیشخوان رستوران‌ها | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | متصدیان ترکیب و آماده‌سازی صنعتی مواد غذایی | اپراتورها و متصدیان دستگاه‌های پخت مواد غذایی | کارگران آماده‌سازی و خردکردن مواد اولیه غذا | پذیرایی‌کنندگان غذا (غیررستورانی) | مدیران خدمات غذا و رستوران | اپراتورهای دستگاه‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و توتون | میزبانان رستوران، سالن پذیرایی و کافه‌ها | سالن‌کاران و گارسون‌ها</t>
+          <t>نانوایان و شیرینی‌پزان | باریستاها | قصابان و برش‌کاران گوشت | آشپزان غذاهای فوری و فست‌فود | آشپزان مراکز پخت گروهی و سلف‌سرویس‌ها | آشپزان منازل مسکونی و سرآشپزان شخصی | آشپزان رستوران | آشپزان غذاهای فوری | کاردان‌ها و تکنسین‌های تغذیه و رژیم‌درمانی | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | کارگران پیشخوان و فست‌فود | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | اپراتورهای ماشین‌آلات پخت مواد غذایی | کارگران آماده‌سازی غذا | سروکنندگان غذا در محیط‌های غیررستورانی | مدیران خدمات پذیرایی و غذا و نوشیدنی | اپراتورهای ماشین‌آلات برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | میزبانان رستوران، سالن پذیرایی و کافی‌شاپ | پیش‌خدمتان و گارسون‌ها</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>سخن گفتن | نظارت | شنیدن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | ریاضیات | نگارش</t>
+          <t>سخن گفتن | نظارت | گوش دادن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | ریاضیات | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | تولید مواد غذایی | زبان انگلیسی | تولید و فرآوری | فروش و بازاریابی | آموزش و تدریس | پرسنلی و منابع انسانی</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | تولید مواد غذایی | زبان انگلیسی | تولید و فرآوری | فروش و بازاریابی | آموزش و پرورش | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | درک کتبی | دید نزدیک | قدرت عضلات تنه | تسهیم توجه | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری طبقه‌بندی | مرتب‌سازی اطلاعات | استدلال استقرایی | روانی بیان ایده‌ها | بیان کتبی | دید دور</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | درک کتبی | بینایی نزدیک | قدرت تنه | تقسیم توجه | توجه انتخابی | تجسم | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | روانی ایده‌ها | بیان کتبی | بینایی دور</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>سرآشپزان و آشپزان ارشد | کارگران سالن پذیرایی، سلف‌سرویس و کمک‌متصدیان بار | کارکنان فست‌فود و پیشخوان رستوران‌ها | سرپرستان رده‌اول مشاغل ساختمانی و استخراج | سرپرستان رده‌اول کارکنان تفریحی و سرگرمی (به‌جز خدمات شرط‌بندی) | سرپرستان رده‌اول کارکنان کشاورزی، صیادی و جنگل‌داری | سرپرستان رده‌اول کمک‌کارگران، کارگران ساده و جابه‌جا‌کنندگان دستی کالا | سرپرستان رده‌اول کارکنان خدمات نظافتی و خانه‌داری | سرپرستان رده‌اول کارکنان فضای سبز، باغبانی و محوطه‌سازی | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و خودروهای جابه‌جایی مواد | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول کارکنان فروش غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان پشتیبانی دفتری و اداری | سرپرستان رده‌اول مهمانداران و متصدیان خدمات مسافری | سرپرستان رده‌اول کارکنان خدمات فردی | سرپرستان رده‌اول کارکنان تولید و عملیات | سرپرستان رده‌اول فروشندگان خرده‌فروشی | کارگران آماده‌سازی و خردکردن مواد اولیه غذا | مدیران خدمات غذا و رستوران | مدیران ارشد اجرایی و عملیاتی</t>
+          <t>سرآشپزان و آشپزان ارشد | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | کارگران پیشخوان و فست‌فود | سرپرستان رده‌اول مشاغل ساختمانی، عمرانی و استخراج | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول مهمانداران و خدمه مسافری | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | سرپرستان رده اول کارگران تولید و عملیات | سرپرستان رده‌اول فروشندگان خرده‌فروشی | کارگران آماده‌سازی غذا | مدیران خدمات پذیرایی و غذا و نوشیدنی | مدیران کل و مدیران عملیات</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال</t>
+          <t>گوش دادن فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | ترابری و حمل‌ونقل | ارتباطات و رسانه‌ها | خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | زبان انگلیسی</t>
+          <t>مدیریت و اداره | حمل و نقل | ارتباطات و رسانه | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | دید نزدیک | مرتب‌سازی اطلاعات | تشخیص گفتار</t>
+          <t>درک شفاهی | بینایی نزدیک | ترتیب‌دهی اطلاعات | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>نانوایان و شیرینی‌پزان | باریستاها | قصابان و خردکنندگان گوشت | سرآشپزان و آشپزان ارشد | آشپزان مراکز پخت گروهی و سلف‌سرویس‌ها | آشپزان منازل مسکونی | آشپزان رستوران‌ها | آشپزان غذاهای فوری | کارگران سالن پذیرایی، سلف‌سرویس و کمک‌متصدیان بار | ظرف‌شویان | کارکنان فست‌فود و پیشخوان رستوران‌ها | متصدیان ترکیب و آماده‌سازی صنعتی مواد غذایی | اپراتورها و متصدیان دستگاه‌های پخت مواد غذایی | کارگران آماده‌سازی و خردکردن مواد اولیه غذا | پذیرایی‌کنندگان غذا (غیررستورانی) | مدیران خدمات غذا و رستوران | اپراتورهای دستگاه‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و توتون | درجه‌بندی‌کنندگان و تفکیک‌کنندگان محصولات کشاورزی | برش‌کاران و پاک‌کنندگان گوشت، مرغ و ماهی | سالن‌کاران و گارسون‌ها</t>
+          <t>نانوایان و شیرینی‌پزان | باریستاها | قصابان و برش‌کاران گوشت | سرآشپزان و آشپزان ارشد | آشپزان مراکز پخت گروهی و سلف‌سرویس‌ها | آشپزان منازل مسکونی و سرآشپزان شخصی | آشپزان رستوران | آشپزان غذاهای فوری | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | ظرف‌شویان | کارگران پیشخوان و فست‌فود | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | اپراتورهای ماشین‌آلات پخت مواد غذایی | کارگران آماده‌سازی غذا | سروکنندگان غذا در محیط‌های غیررستورانی | مدیران خدمات پذیرایی و غذا و نوشیدنی | اپراتورهای ماشین‌آلات برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | برش‌کاران و پاک‌کنندگان گوشت، مرغ و آبزیان | پیش‌خدمتان و گارسون‌ها</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>سخن گفتن | نظارت | تفکر انتقادی | شنیدن فعال</t>
+          <t>سخن گفتن | نظارت | تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | تولید مواد غذایی | خدمات مشتریان و خدمات فردی | ریاضیات | مدیریت و امور اداری | تولید و فرآوری</t>
+          <t>زبان انگلیسی | تولید مواد غذایی | خدمات مشتری و شخصی | ریاضیات | مدیریت و اداره | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | دید نزدیک | وضوح گفتار | حساسیت به مسئله | درک شفاهی | انعطاف‌پذیری طبقه‌بندی | مرتب‌سازی اطلاعات | استدلال قیاسی | تجسم فضایی | استدلال استقرایی | درک کتبی | تشخیص گفتار | قدرت عضلات تنه | چابکی انگشتان | چابکی دستی | ثبات و تسلط دست و بازو | تسهیم توجه | توجه انتخابی</t>
+          <t>بیان شفاهی | بینایی نزدیک | وضوح گفتار | حساسیت به مسئله | درک شفاهی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی | تجسم | استدلال استقرایی | درک کتبی | تشخیص گفتار | قدرت تنه | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | تقسیم توجه | توجه انتخابی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>نانوایان و شیرینی‌پزان | باریستاها | قصابان و خردکنندگان گوشت | سرآشپزان و آشپزان ارشد | آشپزان فست‌فود | آشپزان منازل مسکونی | آشپزان رستوران‌ها | آشپزان غذاهای فوری | کاردان‌های فنی تغذیه | کارگران سالن پذیرایی، سلف‌سرویس و کمک‌متصدیان بار | ظرف‌شویان | کارکنان فست‌فود و پیشخوان رستوران‌ها | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | متصدیان ترکیب و آماده‌سازی صنعتی مواد غذایی | اپراتورها و متصدیان دستگاه‌های پخت مواد غذایی | کارگران آماده‌سازی و خردکردن مواد اولیه غذا | پذیرایی‌کنندگان غذا (غیررستورانی) | مدیران خدمات غذا و رستوران | اپراتورهای دستگاه‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و توتون | سالن‌کاران و گارسون‌ها</t>
+          <t>نانوایان و شیرینی‌پزان | باریستاها | قصابان و برش‌کاران گوشت | سرآشپزان و آشپزان ارشد | آشپزان غذاهای فوری و فست‌فود | آشپزان منازل مسکونی و سرآشپزان شخصی | آشپزان رستوران | آشپزان غذاهای فوری | کاردان‌ها و تکنسین‌های تغذیه و رژیم‌درمانی | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | ظرف‌شویان | کارگران پیشخوان و فست‌فود | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | اپراتورهای ماشین‌آلات پخت مواد غذایی | کارگران آماده‌سازی غذا | سروکنندگان غذا در محیط‌های غیررستورانی | مدیران خدمات پذیرایی و غذا و نوشیدنی | اپراتورهای ماشین‌آلات برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | پیش‌خدمتان و گارسون‌ها</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | سخن گفتن | شنیدن فعال | درک مطلب</t>
+          <t>تفکر انتقادی | نظارت | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | تولید مواد غذایی | فروش و بازاریابی | مدیریت و امور اداری | تولید و فرآوری | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | تولید مواد غذایی | فروش و بازاریابی | مدیریت و اداره | تولید و فرآوری | ریاضیات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>دید نزدیک | روانی بیان ایده‌ها | حساسیت به مسئله | چابکی انگشتان | چابکی دستی | مرتب‌سازی اطلاعات | استدلال قیاسی | بیان شفاهی | خلاقیت و ابتکار | درک کتبی | درک شفاهی | تشخیص گفتار | قدرت عضلات تنه | ثبات و تسلط دست و بازو | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | استدلال استقرایی</t>
+          <t>بینایی نزدیک | روانی ایده‌ها | حساسیت به مسئله | مهارت انگشتان | مهارت دستی | ترتیب‌دهی اطلاعات | استدلال قیاسی | بیان شفاهی | اصالت | درک کتبی | درک شفاهی | تشخیص گفتار | قدرت تنه | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>نانوایان و شیرینی‌پزان | باریستاها | بارتندرهای نوشیدنی سرد | قصابان و خردکنندگان گوشت | سرآشپزان و آشپزان ارشد | آشپزان فست‌فود | آشپزان مراکز پخت گروهی و سلف‌سرویس‌ها | آشپزان رستوران‌ها | آشپزان غذاهای فوری | کاردان‌های فنی تغذیه | کارگران سالن پذیرایی، سلف‌سرویس و کمک‌متصدیان بار | ظرف‌شویان | کارکنان فست‌فود و پیشخوان رستوران‌ها | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | کارگران آماده‌سازی و خردکردن مواد اولیه غذا | دانشمندان و متخصصان صنایع غذایی | پذیرایی‌کنندگان غذا (غیررستورانی) | مدیران خدمات غذا و رستوران | میزبانان رستوران، سالن پذیرایی و کافه‌ها | سالن‌کاران و گارسون‌ها</t>
+          <t>نانوایان و شیرینی‌پزان | باریستاها | متصدیان بار و نوشیدنی | قصابان و برش‌کاران گوشت | سرآشپزان و آشپزان ارشد | آشپزان غذاهای فوری و فست‌فود | آشپزان مراکز پخت گروهی و سلف‌سرویس‌ها | آشپزان رستوران | آشپزان غذاهای فوری | کاردان‌ها و تکنسین‌های تغذیه و رژیم‌درمانی | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | ظرف‌شویان | کارگران پیشخوان و فست‌فود | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | کارگران آماده‌سازی غذا | متخصصان و کارشناسان علوم و صنایع غذایی | سروکنندگان غذا در محیط‌های غیررستورانی | مدیران خدمات پذیرایی و غذا و نوشیدنی | میزبانان رستوران، سالن پذیرایی و کافی‌شاپ | پیش‌خدمتان و گارسون‌ها</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
